--- a/data/trans_dic/P64D$publico_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D$publico_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,0</t>
+          <t>0,81; 3,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,28</t>
+          <t>1,18; 4,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,36</t>
+          <t>1,25; 3,44</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,46</t>
+          <t>1,44; 6,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,9</t>
+          <t>5,01; 9,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,98</t>
+          <t>2,68; 6,95</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,13</t>
+          <t>2,65; 8,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 12,56</t>
+          <t>5,75; 12,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,22</t>
+          <t>4,78; 9,27</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,21; 19,03</t>
+          <t>12,16; 19,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,99; 22,51</t>
+          <t>10,78; 22,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,0; 19,44</t>
+          <t>12,78; 19,32</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 8,06</t>
+          <t>4,11; 8,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,38; 12,15</t>
+          <t>8,21; 11,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,33</t>
+          <t>6,33; 9,28</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2745; 13332</t>
+          <t>2684; 12217</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2896; 11048</t>
+          <t>3034; 10941</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7621; 19835</t>
+          <t>7413; 20360</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11661; 52007</t>
+          <t>11624; 52849</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21571; 39676</t>
+          <t>20076; 38171</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29644; 84145</t>
+          <t>32316; 83817</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9176; 28935</t>
+          <t>9435; 29234</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19145; 40490</t>
+          <t>18528; 40906</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34013; 62547</t>
+          <t>32397; 62877</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57498; 89661</t>
+          <t>57282; 90433</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52730; 107945</t>
+          <t>51697; 109223</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>123551; 184770</t>
+          <t>121470; 183683</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>83786; 158391</t>
+          <t>80741; 158237</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>122483; 177543</t>
+          <t>119889; 174491</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>213515; 319655</t>
+          <t>217072; 317880</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$publico_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D$publico_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,67</t>
+          <t>0,86; 3,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,24</t>
+          <t>1,36; 4,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,44</t>
+          <t>1,34; 3,44</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,56</t>
+          <t>4,64; 9,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,52</t>
+          <t>5,89; 10,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,95</t>
+          <t>5,64; 8,88</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,21</t>
+          <t>3,41; 8,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 12,69</t>
+          <t>7,45; 13,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,27</t>
+          <t>5,8; 10,04</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,16; 19,2</t>
+          <t>13,56; 21,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 22,77</t>
+          <t>17,51; 24,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,78; 19,32</t>
+          <t>16,52; 21,49</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,05</t>
+          <t>6,88; 9,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,94</t>
+          <t>9,91; 12,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,28</t>
+          <t>8,57; 10,66</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>14626</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2684; 12217</t>
+          <t>3147; 13774</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3034; 10941</t>
+          <t>3805; 12767</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7413; 20360</t>
+          <t>8653; 22215</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>32111</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>35454</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61313</t>
+          <t>76751</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11624; 52849</t>
+          <t>29128; 58505</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20076; 38171</t>
+          <t>26310; 46955</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32316; 83817</t>
+          <t>60632; 95482</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>34851</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45594</t>
+          <t>57651</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9435; 29234</t>
+          <t>14229; 36260</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18528; 40906</t>
+          <t>25156; 45922</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32397; 62877</t>
+          <t>43777; 75811</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>72163</t>
+          <t>87289</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>85121</t>
+          <t>95018</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157284</t>
+          <t>182307</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57282; 90433</t>
+          <t>70067; 109084</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51697; 109223</t>
+          <t>78366; 111709</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121470; 183683</t>
+          <t>159332; 207288</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>127982</t>
+          <t>158560</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>148643</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>276625</t>
+          <t>331335</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>80741; 158237</t>
+          <t>132684; 189371</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>119889; 174491</t>
+          <t>149700; 195560</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>217072; 317880</t>
+          <t>294712; 366744</t>
         </is>
       </c>
     </row>
